--- a/06-API-Testing/API-Test-Cases.xlsx
+++ b/06-API-Testing/API-Test-Cases.xlsx
@@ -27,14 +27,13 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -43,24 +42,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
-        <bgColor rgb="001F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D6E4F0"/>
-        <bgColor rgb="00D6E4F0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -68,27 +55,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -457,16 +430,16 @@
   <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="31" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -522,344 +495,484 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>API-001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>/posts/1</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="E2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>Valid JSON post object</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Post object with userId, id, title, body</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>API-Test-Report.md</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>API-002</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>/posts/99999</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" t="n">
         <v>404</v>
       </c>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="F3" t="n">
+        <v>404</v>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>Empty JSON or Not Found error</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Empty object {}</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>API-Test-Report.md</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>API-003</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>/posts</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>{"title": "foo", "body": "bar", "userId": 1}</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>{"title": "QA Test Post", "body": "Testing API", "userId": 1}</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>201</v>
       </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="F4" t="n">
+        <v>201</v>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>Created object with id</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Created object with id: 101</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>API-Test-Report.md</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>API-004</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>/posts</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Invalid JSON</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="n">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>{} (missing fields)</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>400</v>
       </c>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="F5" t="n">
+        <v>201</v>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>Bad Request error</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Mock API returns 201 with id: 101</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>API-Test-Report.md</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>API-005</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>/posts/1</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>{"id": 1, "title": "updated", "body": "bar", "userId": 1}</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>{"id":1,"title":"Updated Title","body":"Updated body","userId":1}</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>200</v>
+      </c>
+      <c r="F6" t="n">
+        <v>200</v>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>Updated object</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Updated object with new title/body</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>API-Test-Report.md</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>API-006</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>PATCH</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>/posts/1</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>{"title": "patched"}</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>200</v>
-      </c>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>{"title":"Patched Title"}</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>200</v>
+      </c>
+      <c r="F7" t="n">
+        <v>200</v>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>Patched object</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
-      <c r="J7" s="3" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Object with modified title</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>API-Test-Report.md</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>API-007</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>DELETE</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>/posts/1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="E8" t="n">
+        <v>200</v>
+      </c>
+      <c r="F8" t="n">
+        <v>200</v>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>Empty response or success</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Empty object {}</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>API-Test-Report.md</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>API-008</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>/users</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="E9" s="3" t="n">
-        <v>200</v>
-      </c>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="E9" t="n">
+        <v>200</v>
+      </c>
+      <c r="F9" t="n">
+        <v>200</v>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>Array of users</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Array of 10 users</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>API-Test-Report.md</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>API-009</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>/users/1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="E10" t="n">
+        <v>200</v>
+      </c>
+      <c r="F10" t="n">
+        <v>200</v>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>User object</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>User object (Leanne Graham)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>API-Test-Report.md</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>API-010</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>/comments?postId=1</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="E11" s="3" t="n">
-        <v>200</v>
-      </c>
-      <c r="F11" s="3" t="inlineStr"/>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="E11" t="n">
+        <v>200</v>
+      </c>
+      <c r="F11" t="n">
+        <v>200</v>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>Array of comments for post 1</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr"/>
-      <c r="J11" s="3" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Array of 5 comments with postId: 1</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>API-Test-Report.md</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
